--- a/Calibracao/Calibracao-modelo.xlsx
+++ b/Calibracao/Calibracao-modelo.xlsx
@@ -1530,11 +1530,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="38541793"/>
-        <c:axId val="57838399"/>
+        <c:axId val="96908228"/>
+        <c:axId val="36543105"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38541793"/>
+        <c:axId val="96908228"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1566,7 +1566,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57838399"/>
+        <c:crossAx val="36543105"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1574,7 +1574,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57838399"/>
+        <c:axId val="36543105"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1614,7 +1614,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38541793"/>
+        <c:crossAx val="96908228"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Calibracao/Calibracao-modelo.xlsx
+++ b/Calibracao/Calibracao-modelo.xlsx
@@ -1530,11 +1530,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="96908228"/>
-        <c:axId val="36543105"/>
+        <c:axId val="73089279"/>
+        <c:axId val="54991646"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="96908228"/>
+        <c:axId val="73089279"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1566,7 +1566,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36543105"/>
+        <c:crossAx val="54991646"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1574,7 +1574,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36543105"/>
+        <c:axId val="54991646"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1614,7 +1614,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96908228"/>
+        <c:crossAx val="73089279"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Calibracao/Calibracao-modelo.xlsx
+++ b/Calibracao/Calibracao-modelo.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Calibrações!$B$1:$O$91</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$Q$31</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$Q$33</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Indústria'!$B$1:$Q$35</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$42</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Instrumentos!$B$1:$R$53</definedName>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="273">
   <si>
     <t xml:space="preserve">Calibração e recursos de medição — Como usar esta planilha</t>
   </si>
@@ -156,13 +156,13 @@
     <t xml:space="preserve">Em dia</t>
   </si>
   <si>
-    <t xml:space="preserve">A próxima data está a mais de 30 dias da data da leitura.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vence em 30 dias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A próxima data está a 30 dias ou menos.</t>
+    <t xml:space="preserve">Até a próxima data faltam mais dias do que o aviso: um quarto do intervalo, com no máximo 30 dias.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vence em breve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faltam menos dias do que o aviso. Na verificação mensal, cerca de uma semana; no intervalo de um ano, 30 dias.</t>
   </si>
   <si>
     <t xml:space="preserve">Vencido</t>
@@ -492,7 +492,7 @@
     <t xml:space="preserve">Da aba Instrumentos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vencem em mais de 30 dias.</t>
+    <t xml:space="preserve">Mais longe do que o aviso: um quarto do intervalo, no máximo 30 dias.</t>
   </si>
   <si>
     <t xml:space="preserve">Programar a calibração ou a verificação.</t>
@@ -699,6 +699,12 @@
     <t xml:space="preserve">Temperatura dos insumos refrigerados: até 7 °C</t>
   </si>
   <si>
+    <t xml:space="preserve">TER-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termômetro de visor da câmara fria, novo</t>
+  </si>
+  <si>
     <t xml:space="preserve">BAL-01</t>
   </si>
   <si>
@@ -768,7 +774,10 @@
     <t xml:space="preserve">Planilha de verificação FR-07 · Contra o TER-01, a 5 °C</t>
   </si>
   <si>
-    <t xml:space="preserve">Retirado da câmara. Um termômetro novo, verificado contra o TER-01, foi instalado no lugar.</t>
+    <t xml:space="preserve">Retirado da câmara. O TER-05, verificado contra o TER-01, foi instalado no lugar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TER-05 · Termômetro de visor da câmara fria, novo</t>
   </si>
   <si>
     <t xml:space="preserve">Instrumentos por situação</t>
@@ -1489,7 +1498,7 @@
                   <c:v>Em dia</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Vence em 30 dias</c:v>
+                  <c:v>Vence em breve</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Vencido</c:v>
@@ -1530,11 +1539,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="73089279"/>
-        <c:axId val="54991646"/>
+        <c:axId val="7906842"/>
+        <c:axId val="70901307"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="73089279"/>
+        <c:axId val="7906842"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1566,7 +1575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54991646"/>
+        <c:crossAx val="70901307"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1574,7 +1583,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54991646"/>
+        <c:axId val="70901307"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1614,7 +1623,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73089279"/>
+        <c:crossAx val="7906842"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1940,7 +1949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
         <v>16</v>
       </c>
@@ -1948,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
         <v>18</v>
       </c>
@@ -2376,7 +2385,7 @@
         <v/>
       </c>
       <c r="P8" s="16" t="str">
-        <f aca="false">IF(C8="","",IF(N8="Não","Fora de uso",IF(L8="","Sem calibração",IF(AND(ISNUMBER($E$4),O8&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O8-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C8="","",IF(N8="Não","Fora de uso",IF(L8="","Sem calibração",IF(AND(ISNUMBER($E$4),O8&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O8-$E$4&lt;MIN(30,(O8-L8)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q8" s="17" t="str">
@@ -2409,7 +2418,7 @@
         <v/>
       </c>
       <c r="P9" s="16" t="str">
-        <f aca="false">IF(C9="","",IF(N9="Não","Fora de uso",IF(L9="","Sem calibração",IF(AND(ISNUMBER($E$4),O9&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O9-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C9="","",IF(N9="Não","Fora de uso",IF(L9="","Sem calibração",IF(AND(ISNUMBER($E$4),O9&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O9-$E$4&lt;MIN(30,(O9-L9)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q9" s="17" t="str">
@@ -2442,7 +2451,7 @@
         <v/>
       </c>
       <c r="P10" s="16" t="str">
-        <f aca="false">IF(C10="","",IF(N10="Não","Fora de uso",IF(L10="","Sem calibração",IF(AND(ISNUMBER($E$4),O10&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O10-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C10="","",IF(N10="Não","Fora de uso",IF(L10="","Sem calibração",IF(AND(ISNUMBER($E$4),O10&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O10-$E$4&lt;MIN(30,(O10-L10)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q10" s="17" t="str">
@@ -2475,7 +2484,7 @@
         <v/>
       </c>
       <c r="P11" s="16" t="str">
-        <f aca="false">IF(C11="","",IF(N11="Não","Fora de uso",IF(L11="","Sem calibração",IF(AND(ISNUMBER($E$4),O11&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O11-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C11="","",IF(N11="Não","Fora de uso",IF(L11="","Sem calibração",IF(AND(ISNUMBER($E$4),O11&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O11-$E$4&lt;MIN(30,(O11-L11)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q11" s="17" t="str">
@@ -2508,7 +2517,7 @@
         <v/>
       </c>
       <c r="P12" s="16" t="str">
-        <f aca="false">IF(C12="","",IF(N12="Não","Fora de uso",IF(L12="","Sem calibração",IF(AND(ISNUMBER($E$4),O12&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O12-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C12="","",IF(N12="Não","Fora de uso",IF(L12="","Sem calibração",IF(AND(ISNUMBER($E$4),O12&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O12-$E$4&lt;MIN(30,(O12-L12)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q12" s="17" t="str">
@@ -2541,7 +2550,7 @@
         <v/>
       </c>
       <c r="P13" s="16" t="str">
-        <f aca="false">IF(C13="","",IF(N13="Não","Fora de uso",IF(L13="","Sem calibração",IF(AND(ISNUMBER($E$4),O13&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O13-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C13="","",IF(N13="Não","Fora de uso",IF(L13="","Sem calibração",IF(AND(ISNUMBER($E$4),O13&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O13-$E$4&lt;MIN(30,(O13-L13)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q13" s="17" t="str">
@@ -2574,7 +2583,7 @@
         <v/>
       </c>
       <c r="P14" s="16" t="str">
-        <f aca="false">IF(C14="","",IF(N14="Não","Fora de uso",IF(L14="","Sem calibração",IF(AND(ISNUMBER($E$4),O14&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O14-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C14="","",IF(N14="Não","Fora de uso",IF(L14="","Sem calibração",IF(AND(ISNUMBER($E$4),O14&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O14-$E$4&lt;MIN(30,(O14-L14)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q14" s="17" t="str">
@@ -2607,7 +2616,7 @@
         <v/>
       </c>
       <c r="P15" s="16" t="str">
-        <f aca="false">IF(C15="","",IF(N15="Não","Fora de uso",IF(L15="","Sem calibração",IF(AND(ISNUMBER($E$4),O15&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O15-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C15="","",IF(N15="Não","Fora de uso",IF(L15="","Sem calibração",IF(AND(ISNUMBER($E$4),O15&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O15-$E$4&lt;MIN(30,(O15-L15)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q15" s="17" t="str">
@@ -2640,7 +2649,7 @@
         <v/>
       </c>
       <c r="P16" s="16" t="str">
-        <f aca="false">IF(C16="","",IF(N16="Não","Fora de uso",IF(L16="","Sem calibração",IF(AND(ISNUMBER($E$4),O16&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O16-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C16="","",IF(N16="Não","Fora de uso",IF(L16="","Sem calibração",IF(AND(ISNUMBER($E$4),O16&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O16-$E$4&lt;MIN(30,(O16-L16)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q16" s="17" t="str">
@@ -2673,7 +2682,7 @@
         <v/>
       </c>
       <c r="P17" s="16" t="str">
-        <f aca="false">IF(C17="","",IF(N17="Não","Fora de uso",IF(L17="","Sem calibração",IF(AND(ISNUMBER($E$4),O17&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O17-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C17="","",IF(N17="Não","Fora de uso",IF(L17="","Sem calibração",IF(AND(ISNUMBER($E$4),O17&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O17-$E$4&lt;MIN(30,(O17-L17)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q17" s="17" t="str">
@@ -2706,7 +2715,7 @@
         <v/>
       </c>
       <c r="P18" s="16" t="str">
-        <f aca="false">IF(C18="","",IF(N18="Não","Fora de uso",IF(L18="","Sem calibração",IF(AND(ISNUMBER($E$4),O18&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O18-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C18="","",IF(N18="Não","Fora de uso",IF(L18="","Sem calibração",IF(AND(ISNUMBER($E$4),O18&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O18-$E$4&lt;MIN(30,(O18-L18)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q18" s="17" t="str">
@@ -2739,7 +2748,7 @@
         <v/>
       </c>
       <c r="P19" s="16" t="str">
-        <f aca="false">IF(C19="","",IF(N19="Não","Fora de uso",IF(L19="","Sem calibração",IF(AND(ISNUMBER($E$4),O19&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O19-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C19="","",IF(N19="Não","Fora de uso",IF(L19="","Sem calibração",IF(AND(ISNUMBER($E$4),O19&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O19-$E$4&lt;MIN(30,(O19-L19)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q19" s="17" t="str">
@@ -2772,7 +2781,7 @@
         <v/>
       </c>
       <c r="P20" s="16" t="str">
-        <f aca="false">IF(C20="","",IF(N20="Não","Fora de uso",IF(L20="","Sem calibração",IF(AND(ISNUMBER($E$4),O20&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O20-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C20="","",IF(N20="Não","Fora de uso",IF(L20="","Sem calibração",IF(AND(ISNUMBER($E$4),O20&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O20-$E$4&lt;MIN(30,(O20-L20)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q20" s="17" t="str">
@@ -2805,7 +2814,7 @@
         <v/>
       </c>
       <c r="P21" s="16" t="str">
-        <f aca="false">IF(C21="","",IF(N21="Não","Fora de uso",IF(L21="","Sem calibração",IF(AND(ISNUMBER($E$4),O21&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O21-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C21="","",IF(N21="Não","Fora de uso",IF(L21="","Sem calibração",IF(AND(ISNUMBER($E$4),O21&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O21-$E$4&lt;MIN(30,(O21-L21)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q21" s="17" t="str">
@@ -2838,7 +2847,7 @@
         <v/>
       </c>
       <c r="P22" s="16" t="str">
-        <f aca="false">IF(C22="","",IF(N22="Não","Fora de uso",IF(L22="","Sem calibração",IF(AND(ISNUMBER($E$4),O22&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O22-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C22="","",IF(N22="Não","Fora de uso",IF(L22="","Sem calibração",IF(AND(ISNUMBER($E$4),O22&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O22-$E$4&lt;MIN(30,(O22-L22)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q22" s="17" t="str">
@@ -2871,7 +2880,7 @@
         <v/>
       </c>
       <c r="P23" s="16" t="str">
-        <f aca="false">IF(C23="","",IF(N23="Não","Fora de uso",IF(L23="","Sem calibração",IF(AND(ISNUMBER($E$4),O23&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O23-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C23="","",IF(N23="Não","Fora de uso",IF(L23="","Sem calibração",IF(AND(ISNUMBER($E$4),O23&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O23-$E$4&lt;MIN(30,(O23-L23)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q23" s="17" t="str">
@@ -2904,7 +2913,7 @@
         <v/>
       </c>
       <c r="P24" s="16" t="str">
-        <f aca="false">IF(C24="","",IF(N24="Não","Fora de uso",IF(L24="","Sem calibração",IF(AND(ISNUMBER($E$4),O24&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O24-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C24="","",IF(N24="Não","Fora de uso",IF(L24="","Sem calibração",IF(AND(ISNUMBER($E$4),O24&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O24-$E$4&lt;MIN(30,(O24-L24)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q24" s="17" t="str">
@@ -2937,7 +2946,7 @@
         <v/>
       </c>
       <c r="P25" s="16" t="str">
-        <f aca="false">IF(C25="","",IF(N25="Não","Fora de uso",IF(L25="","Sem calibração",IF(AND(ISNUMBER($E$4),O25&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O25-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C25="","",IF(N25="Não","Fora de uso",IF(L25="","Sem calibração",IF(AND(ISNUMBER($E$4),O25&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O25-$E$4&lt;MIN(30,(O25-L25)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q25" s="17" t="str">
@@ -2970,7 +2979,7 @@
         <v/>
       </c>
       <c r="P26" s="16" t="str">
-        <f aca="false">IF(C26="","",IF(N26="Não","Fora de uso",IF(L26="","Sem calibração",IF(AND(ISNUMBER($E$4),O26&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O26-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C26="","",IF(N26="Não","Fora de uso",IF(L26="","Sem calibração",IF(AND(ISNUMBER($E$4),O26&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O26-$E$4&lt;MIN(30,(O26-L26)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q26" s="17" t="str">
@@ -3003,7 +3012,7 @@
         <v/>
       </c>
       <c r="P27" s="16" t="str">
-        <f aca="false">IF(C27="","",IF(N27="Não","Fora de uso",IF(L27="","Sem calibração",IF(AND(ISNUMBER($E$4),O27&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O27-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C27="","",IF(N27="Não","Fora de uso",IF(L27="","Sem calibração",IF(AND(ISNUMBER($E$4),O27&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O27-$E$4&lt;MIN(30,(O27-L27)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q27" s="17" t="str">
@@ -3036,7 +3045,7 @@
         <v/>
       </c>
       <c r="P28" s="16" t="str">
-        <f aca="false">IF(C28="","",IF(N28="Não","Fora de uso",IF(L28="","Sem calibração",IF(AND(ISNUMBER($E$4),O28&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O28-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C28="","",IF(N28="Não","Fora de uso",IF(L28="","Sem calibração",IF(AND(ISNUMBER($E$4),O28&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O28-$E$4&lt;MIN(30,(O28-L28)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q28" s="17" t="str">
@@ -3069,7 +3078,7 @@
         <v/>
       </c>
       <c r="P29" s="16" t="str">
-        <f aca="false">IF(C29="","",IF(N29="Não","Fora de uso",IF(L29="","Sem calibração",IF(AND(ISNUMBER($E$4),O29&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O29-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C29="","",IF(N29="Não","Fora de uso",IF(L29="","Sem calibração",IF(AND(ISNUMBER($E$4),O29&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O29-$E$4&lt;MIN(30,(O29-L29)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q29" s="17" t="str">
@@ -3102,7 +3111,7 @@
         <v/>
       </c>
       <c r="P30" s="16" t="str">
-        <f aca="false">IF(C30="","",IF(N30="Não","Fora de uso",IF(L30="","Sem calibração",IF(AND(ISNUMBER($E$4),O30&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O30-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C30="","",IF(N30="Não","Fora de uso",IF(L30="","Sem calibração",IF(AND(ISNUMBER($E$4),O30&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O30-$E$4&lt;MIN(30,(O30-L30)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q30" s="17" t="str">
@@ -3135,7 +3144,7 @@
         <v/>
       </c>
       <c r="P31" s="16" t="str">
-        <f aca="false">IF(C31="","",IF(N31="Não","Fora de uso",IF(L31="","Sem calibração",IF(AND(ISNUMBER($E$4),O31&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O31-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C31="","",IF(N31="Não","Fora de uso",IF(L31="","Sem calibração",IF(AND(ISNUMBER($E$4),O31&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O31-$E$4&lt;MIN(30,(O31-L31)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q31" s="17" t="str">
@@ -3168,7 +3177,7 @@
         <v/>
       </c>
       <c r="P32" s="16" t="str">
-        <f aca="false">IF(C32="","",IF(N32="Não","Fora de uso",IF(L32="","Sem calibração",IF(AND(ISNUMBER($E$4),O32&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O32-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C32="","",IF(N32="Não","Fora de uso",IF(L32="","Sem calibração",IF(AND(ISNUMBER($E$4),O32&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O32-$E$4&lt;MIN(30,(O32-L32)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q32" s="17" t="str">
@@ -3201,7 +3210,7 @@
         <v/>
       </c>
       <c r="P33" s="16" t="str">
-        <f aca="false">IF(C33="","",IF(N33="Não","Fora de uso",IF(L33="","Sem calibração",IF(AND(ISNUMBER($E$4),O33&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O33-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C33="","",IF(N33="Não","Fora de uso",IF(L33="","Sem calibração",IF(AND(ISNUMBER($E$4),O33&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O33-$E$4&lt;MIN(30,(O33-L33)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q33" s="17" t="str">
@@ -3234,7 +3243,7 @@
         <v/>
       </c>
       <c r="P34" s="16" t="str">
-        <f aca="false">IF(C34="","",IF(N34="Não","Fora de uso",IF(L34="","Sem calibração",IF(AND(ISNUMBER($E$4),O34&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O34-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C34="","",IF(N34="Não","Fora de uso",IF(L34="","Sem calibração",IF(AND(ISNUMBER($E$4),O34&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O34-$E$4&lt;MIN(30,(O34-L34)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q34" s="17" t="str">
@@ -3267,7 +3276,7 @@
         <v/>
       </c>
       <c r="P35" s="16" t="str">
-        <f aca="false">IF(C35="","",IF(N35="Não","Fora de uso",IF(L35="","Sem calibração",IF(AND(ISNUMBER($E$4),O35&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O35-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C35="","",IF(N35="Não","Fora de uso",IF(L35="","Sem calibração",IF(AND(ISNUMBER($E$4),O35&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O35-$E$4&lt;MIN(30,(O35-L35)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q35" s="17" t="str">
@@ -3300,7 +3309,7 @@
         <v/>
       </c>
       <c r="P36" s="16" t="str">
-        <f aca="false">IF(C36="","",IF(N36="Não","Fora de uso",IF(L36="","Sem calibração",IF(AND(ISNUMBER($E$4),O36&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O36-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C36="","",IF(N36="Não","Fora de uso",IF(L36="","Sem calibração",IF(AND(ISNUMBER($E$4),O36&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O36-$E$4&lt;MIN(30,(O36-L36)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q36" s="17" t="str">
@@ -3333,7 +3342,7 @@
         <v/>
       </c>
       <c r="P37" s="16" t="str">
-        <f aca="false">IF(C37="","",IF(N37="Não","Fora de uso",IF(L37="","Sem calibração",IF(AND(ISNUMBER($E$4),O37&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O37-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C37="","",IF(N37="Não","Fora de uso",IF(L37="","Sem calibração",IF(AND(ISNUMBER($E$4),O37&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O37-$E$4&lt;MIN(30,(O37-L37)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q37" s="17" t="str">
@@ -3366,7 +3375,7 @@
         <v/>
       </c>
       <c r="P38" s="16" t="str">
-        <f aca="false">IF(C38="","",IF(N38="Não","Fora de uso",IF(L38="","Sem calibração",IF(AND(ISNUMBER($E$4),O38&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O38-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C38="","",IF(N38="Não","Fora de uso",IF(L38="","Sem calibração",IF(AND(ISNUMBER($E$4),O38&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O38-$E$4&lt;MIN(30,(O38-L38)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q38" s="17" t="str">
@@ -3399,7 +3408,7 @@
         <v/>
       </c>
       <c r="P39" s="16" t="str">
-        <f aca="false">IF(C39="","",IF(N39="Não","Fora de uso",IF(L39="","Sem calibração",IF(AND(ISNUMBER($E$4),O39&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O39-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C39="","",IF(N39="Não","Fora de uso",IF(L39="","Sem calibração",IF(AND(ISNUMBER($E$4),O39&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O39-$E$4&lt;MIN(30,(O39-L39)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q39" s="17" t="str">
@@ -3432,7 +3441,7 @@
         <v/>
       </c>
       <c r="P40" s="16" t="str">
-        <f aca="false">IF(C40="","",IF(N40="Não","Fora de uso",IF(L40="","Sem calibração",IF(AND(ISNUMBER($E$4),O40&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O40-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C40="","",IF(N40="Não","Fora de uso",IF(L40="","Sem calibração",IF(AND(ISNUMBER($E$4),O40&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O40-$E$4&lt;MIN(30,(O40-L40)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q40" s="17" t="str">
@@ -3465,7 +3474,7 @@
         <v/>
       </c>
       <c r="P41" s="16" t="str">
-        <f aca="false">IF(C41="","",IF(N41="Não","Fora de uso",IF(L41="","Sem calibração",IF(AND(ISNUMBER($E$4),O41&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O41-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C41="","",IF(N41="Não","Fora de uso",IF(L41="","Sem calibração",IF(AND(ISNUMBER($E$4),O41&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O41-$E$4&lt;MIN(30,(O41-L41)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q41" s="17" t="str">
@@ -3498,7 +3507,7 @@
         <v/>
       </c>
       <c r="P42" s="16" t="str">
-        <f aca="false">IF(C42="","",IF(N42="Não","Fora de uso",IF(L42="","Sem calibração",IF(AND(ISNUMBER($E$4),O42&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O42-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C42="","",IF(N42="Não","Fora de uso",IF(L42="","Sem calibração",IF(AND(ISNUMBER($E$4),O42&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O42-$E$4&lt;MIN(30,(O42-L42)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q42" s="17" t="str">
@@ -3531,7 +3540,7 @@
         <v/>
       </c>
       <c r="P43" s="16" t="str">
-        <f aca="false">IF(C43="","",IF(N43="Não","Fora de uso",IF(L43="","Sem calibração",IF(AND(ISNUMBER($E$4),O43&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O43-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C43="","",IF(N43="Não","Fora de uso",IF(L43="","Sem calibração",IF(AND(ISNUMBER($E$4),O43&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O43-$E$4&lt;MIN(30,(O43-L43)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q43" s="17" t="str">
@@ -3564,7 +3573,7 @@
         <v/>
       </c>
       <c r="P44" s="16" t="str">
-        <f aca="false">IF(C44="","",IF(N44="Não","Fora de uso",IF(L44="","Sem calibração",IF(AND(ISNUMBER($E$4),O44&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O44-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C44="","",IF(N44="Não","Fora de uso",IF(L44="","Sem calibração",IF(AND(ISNUMBER($E$4),O44&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O44-$E$4&lt;MIN(30,(O44-L44)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q44" s="17" t="str">
@@ -3597,7 +3606,7 @@
         <v/>
       </c>
       <c r="P45" s="16" t="str">
-        <f aca="false">IF(C45="","",IF(N45="Não","Fora de uso",IF(L45="","Sem calibração",IF(AND(ISNUMBER($E$4),O45&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O45-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C45="","",IF(N45="Não","Fora de uso",IF(L45="","Sem calibração",IF(AND(ISNUMBER($E$4),O45&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O45-$E$4&lt;MIN(30,(O45-L45)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q45" s="17" t="str">
@@ -3630,7 +3639,7 @@
         <v/>
       </c>
       <c r="P46" s="16" t="str">
-        <f aca="false">IF(C46="","",IF(N46="Não","Fora de uso",IF(L46="","Sem calibração",IF(AND(ISNUMBER($E$4),O46&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O46-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C46="","",IF(N46="Não","Fora de uso",IF(L46="","Sem calibração",IF(AND(ISNUMBER($E$4),O46&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O46-$E$4&lt;MIN(30,(O46-L46)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q46" s="17" t="str">
@@ -3663,7 +3672,7 @@
         <v/>
       </c>
       <c r="P47" s="16" t="str">
-        <f aca="false">IF(C47="","",IF(N47="Não","Fora de uso",IF(L47="","Sem calibração",IF(AND(ISNUMBER($E$4),O47&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O47-$E$4&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(C47="","",IF(N47="Não","Fora de uso",IF(L47="","Sem calibração",IF(AND(ISNUMBER($E$4),O47&lt;$E$4),"Vencido",IF(AND(ISNUMBER($E$4),O47-$E$4&lt;MIN(30,(O47-L47)/4)),"Vence em breve","Em dia")))))</f>
         <v/>
       </c>
       <c r="Q47" s="17" t="str">
@@ -3727,8 +3736,8 @@
       <c r="C51" s="19"/>
       <c r="D51" s="19"/>
       <c r="E51" s="21" t="str">
-        <f aca="false">COUNTIF(P8:P47,"Em dia")&amp;" em dia"&amp;", "&amp;COUNTIF(P8:P47,"Vence em 30 dias")&amp;" vence em 30 dias"&amp;", "&amp;COUNTIF(P8:P47,"Vencido")&amp;" vencido"&amp;", "&amp;COUNTIF(P8:P47,"Sem calibração")&amp;" sem calibração"&amp;", "&amp;COUNTIF(P8:P47,"Fora de uso")&amp;" fora de uso"</f>
-        <v>0 em dia, 0 vence em 30 dias, 0 vencido, 0 sem calibração, 0 fora de uso</v>
+        <f aca="false">COUNTIF(P8:P47,"Em dia")&amp;" em dia"&amp;", "&amp;COUNTIF(P8:P47,"Vence em breve")&amp;" vence em breve"&amp;", "&amp;COUNTIF(P8:P47,"Vencido")&amp;" vencido"&amp;", "&amp;COUNTIF(P8:P47,"Sem calibração")&amp;" sem calibração"&amp;", "&amp;COUNTIF(P8:P47,"Fora de uso")&amp;" fora de uso"</f>
+        <v>0 em dia, 0 vence em breve, 0 vencido, 0 sem calibração, 0 fora de uso</v>
       </c>
       <c r="F51" s="21"/>
       <c r="G51" s="21"/>
@@ -3775,7 +3784,7 @@
       <c r="C53" s="19"/>
       <c r="D53" s="19"/>
       <c r="E53" s="21" t="str">
-        <f aca="false">IF(E50=0,"Cadastre os instrumentos",IF(E4="","Informe a data da leitura",IF(COUNTIF(P8:P47,"Vencido")&gt;0,"Há instrumento vencido: bloquear até calibrar",IF(COUNTIF(P8:P47,"Sem calibração")&gt;0,"Há instrumento sem calibração ou verificação",IF(COUNTIF(Q8:Q47,"Resolução grossa")&gt;0,"Há instrumento com resolução grossa para a tolerância",IF(COUNTIF(P8:P47,"Vence em 30 dias")&gt;0,"Há instrumento que vence em 30 dias: programe",IF(SUMPRODUCT((R8:R47&lt;&gt;"")*(R8:R47&lt;&gt;"OK")*(R8:R47&lt;&gt;"Fora de uso"))&gt;0,"Há instrumento a completar: veja a coluna Conferência","OK")))))))</f>
+        <f aca="false">IF(E50=0,"Cadastre os instrumentos",IF(E4="","Informe a data da leitura",IF(COUNTIF(P8:P47,"Vencido")&gt;0,"Há instrumento vencido: bloquear até calibrar",IF(COUNTIF(P8:P47,"Sem calibração")&gt;0,"Há instrumento sem calibração ou verificação",IF(COUNTIF(Q8:Q47,"Resolução grossa")&gt;0,"Há instrumento com resolução grossa para a tolerância",IF(COUNTIF(P8:P47,"Vence em breve")&gt;0,"Há instrumento que vence em breve: programe",IF(SUMPRODUCT((R8:R47&lt;&gt;"")*(R8:R47&lt;&gt;"OK")*(R8:R47&lt;&gt;"Fora de uso"))&gt;0,"Há instrumento a completar: veja a coluna Conferência","OK")))))))</f>
         <v>Cadastre os instrumentos</v>
       </c>
       <c r="F53" s="21"/>
@@ -3813,7 +3822,7 @@
       <formula>P8="Em dia"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>P8="Vence em 30 dias"</formula>
+      <formula>P8="Vence em breve"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>P8="Vencido"</formula>
@@ -6713,7 +6722,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="25" t="n">
-        <f aca="false">COUNTIF(Instrumentos!P8:P47,"Vence em 30 dias")</f>
+        <f aca="false">COUNTIF(Instrumentos!P8:P47,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="D8" s="26" t="s">
@@ -6848,7 +6857,7 @@
         <v>97</v>
       </c>
       <c r="C19" s="21" t="str">
-        <f aca="false">IF(C6=0,"Cadastre os instrumentos na aba Instrumentos",IF(C3="","Informe a data da leitura na aba Instrumentos",IF(C15&gt;0,"Há reprovado sem a avaliação dos resultados anteriores",IF(C9&gt;0,"Há instrumento vencido: bloquear até calibrar",IF(C10&gt;0,"Há instrumento sem calibração ou verificação",IF(C12&gt;0,"Há instrumento com resolução grossa para a tolerância",IF(C8&gt;0,"Há instrumento que vence em 30 dias: programe",IF(C16&gt;0,"Há registro a completar","OK"))))))))</f>
+        <f aca="false">IF(C6=0,"Cadastre os instrumentos na aba Instrumentos",IF(C3="","Informe a data da leitura na aba Instrumentos",IF(C15&gt;0,"Há reprovado sem a avaliação dos resultados anteriores",IF(C9&gt;0,"Há instrumento vencido: bloquear até calibrar",IF(C10&gt;0,"Há instrumento sem calibração ou verificação",IF(C12&gt;0,"Há instrumento com resolução grossa para a tolerância",IF(C8&gt;0,"Há instrumento que vence em breve: programe",IF(C16&gt;0,"Há registro a completar","OK"))))))))</f>
         <v>Cadastre os instrumentos na aba Instrumentos</v>
       </c>
       <c r="D19" s="21"/>
@@ -7218,7 +7227,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:Q31"/>
+  <dimension ref="B1:Q33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -7488,8 +7497,8 @@
         <v>46482</v>
       </c>
       <c r="O12" s="16" t="str">
-        <f aca="false">IF(B12="","",IF(M12="Não","Fora de uso",IF(K12="","Sem calibração",IF(AND(ISNUMBER($D$8),N12&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N12-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
-        <v>Vence em 30 dias</v>
+        <f aca="false">IF(B12="","",IF(M12="Não","Fora de uso",IF(K12="","Sem calibração",IF(AND(ISNUMBER($D$8),N12&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N12-$D$8&lt;MIN(30,(N12-K12)/4)),"Vence em breve","Em dia")))))</f>
+        <v>Vence em breve</v>
       </c>
       <c r="P12" s="17" t="str">
         <f aca="false">IF(OR(G12="",H12=""),"",IF(H12&lt;=G12/10+0.000000001,"Adequado","Resolução grossa"))</f>
@@ -7542,7 +7551,7 @@
         <v>46553</v>
       </c>
       <c r="O13" s="16" t="str">
-        <f aca="false">IF(B13="","",IF(M13="Não","Fora de uso",IF(K13="","Sem calibração",IF(AND(ISNUMBER($D$8),N13&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N13-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B13="","",IF(M13="Não","Fora de uso",IF(K13="","Sem calibração",IF(AND(ISNUMBER($D$8),N13&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N13-$D$8&lt;MIN(30,(N13-K13)/4)),"Vence em breve","Em dia")))))</f>
         <v>Fora de uso</v>
       </c>
       <c r="P13" s="17" t="str">
@@ -7596,7 +7605,7 @@
         <v>46553</v>
       </c>
       <c r="O14" s="16" t="str">
-        <f aca="false">IF(B14="","",IF(M14="Não","Fora de uso",IF(K14="","Sem calibração",IF(AND(ISNUMBER($D$8),N14&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N14-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B14="","",IF(M14="Não","Fora de uso",IF(K14="","Sem calibração",IF(AND(ISNUMBER($D$8),N14&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N14-$D$8&lt;MIN(30,(N14-K14)/4)),"Vence em breve","Em dia")))))</f>
         <v>Em dia</v>
       </c>
       <c r="P14" s="17" t="str">
@@ -7648,7 +7657,7 @@
         <v/>
       </c>
       <c r="O15" s="16" t="str">
-        <f aca="false">IF(B15="","",IF(M15="Não","Fora de uso",IF(K15="","Sem calibração",IF(AND(ISNUMBER($D$8),N15&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N15-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B15="","",IF(M15="Não","Fora de uso",IF(K15="","Sem calibração",IF(AND(ISNUMBER($D$8),N15&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N15-$D$8&lt;MIN(30,(N15-K15)/4)),"Vence em breve","Em dia")))))</f>
         <v>Sem calibração</v>
       </c>
       <c r="P15" s="17" t="str">
@@ -7668,42 +7677,42 @@
         <v>199</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="G16" s="35" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H16" s="35" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I16" s="36" t="s">
         <v>182</v>
       </c>
       <c r="J16" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="37" t="n">
+        <v>46461</v>
+      </c>
+      <c r="L16" s="35" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" s="37" t="n">
-        <v>46447</v>
-      </c>
-      <c r="L16" s="35" t="n">
-        <v>2</v>
       </c>
       <c r="M16" s="34" t="s">
         <v>183</v>
       </c>
       <c r="N16" s="15" t="n">
         <f aca="false">IF(OR(K16="",J16=""),"",EDATE(K16,J16))</f>
-        <v>46478</v>
+        <v>46553</v>
       </c>
       <c r="O16" s="16" t="str">
-        <f aca="false">IF(B16="","",IF(M16="Não","Fora de uso",IF(K16="","Sem calibração",IF(AND(ISNUMBER($D$8),N16&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N16-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
-        <v>Vence em 30 dias</v>
+        <f aca="false">IF(B16="","",IF(M16="Não","Fora de uso",IF(K16="","Sem calibração",IF(AND(ISNUMBER($D$8),N16&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N16-$D$8&lt;MIN(30,(N16-K16)/4)),"Vence em breve","Em dia")))))</f>
+        <v>Em dia</v>
       </c>
       <c r="P16" s="17" t="str">
         <f aca="false">IF(OR(G16="",H16=""),"",IF(H16&lt;=G16/10+0.000000001,"Adequado","Resolução grossa"))</f>
@@ -7714,50 +7723,50 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="F17" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>202</v>
-      </c>
       <c r="G17" s="35" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="H17" s="35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="J17" s="34" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K17" s="37" t="n">
-        <v>46407</v>
+        <v>46447</v>
       </c>
       <c r="L17" s="35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M17" s="34" t="s">
         <v>183</v>
       </c>
       <c r="N17" s="15" t="n">
         <f aca="false">IF(OR(K17="",J17=""),"",EDATE(K17,J17))</f>
-        <v>46772</v>
+        <v>46478</v>
       </c>
       <c r="O17" s="16" t="str">
-        <f aca="false">IF(B17="","",IF(M17="Não","Fora de uso",IF(K17="","Sem calibração",IF(AND(ISNUMBER($D$8),N17&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N17-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
-        <v>Em dia</v>
+        <f aca="false">IF(B17="","",IF(M17="Não","Fora de uso",IF(K17="","Sem calibração",IF(AND(ISNUMBER($D$8),N17&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N17-$D$8&lt;MIN(30,(N17-K17)/4)),"Vence em breve","Em dia")))))</f>
+        <v>Vence em breve</v>
       </c>
       <c r="P17" s="17" t="str">
         <f aca="false">IF(OR(G17="",H17=""),"",IF(H17&lt;=G17/10+0.000000001,"Adequado","Resolução grossa"))</f>
@@ -7768,128 +7777,143 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="38" t="s">
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>200</v>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" s="37" t="n">
+        <v>46407</v>
+      </c>
+      <c r="L18" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="M18" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="N18" s="15" t="n">
+        <f aca="false">IF(OR(K18="",J18=""),"",EDATE(K18,J18))</f>
+        <v>46772</v>
+      </c>
+      <c r="O18" s="16" t="str">
+        <f aca="false">IF(B18="","",IF(M18="Não","Fora de uso",IF(K18="","Sem calibração",IF(AND(ISNUMBER($D$8),N18&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N18-$D$8&lt;MIN(30,(N18-K18)/4)),"Vence em breve","Em dia")))))</f>
+        <v>Em dia</v>
+      </c>
+      <c r="P18" s="17" t="str">
+        <f aca="false">IF(OR(G18="",H18=""),"",IF(H18&lt;=G18/10+0.000000001,"Adequado","Resolução grossa"))</f>
+        <v>Adequado</v>
+      </c>
+      <c r="Q18" s="17" t="str">
+        <f aca="false">IF(B18="","",IF(E18="","Falta o que mede",IF(I18="","Falta o tipo de controle",IF(J18="","Falta o intervalo",IF(L18="","Falta o erro máximo admissível",IF(O18="Fora de uso","Fora de uso",IF(O18="Vencido","Vencido: bloquear ou calibrar",IF(O18="Sem calibração","Sem calibração ou verificação",IF(P18="Resolução grossa","Resolução grossa para a tolerância","OK")))))))))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="25" t="s">
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="D20" s="25" t="s">
+      <c r="C21" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="D21" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="25" t="s">
+      <c r="E21" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="F21" s="39"/>
+      <c r="G21" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="25" t="s">
+      <c r="H21" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="I20" s="25" t="s">
+      <c r="I21" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="J20" s="39" t="s">
+      <c r="J21" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39" t="s">
-        <v>208</v>
-      </c>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="25" t="s">
+      <c r="K21" s="39"/>
+      <c r="L21" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="25" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="37" t="n">
-        <v>46188</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>211</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I21" s="23" t="n">
-        <f aca="false">IFERROR(INDEX($L$12:$L$17,MATCH(LEFT(C21,FIND(" ·",C21)-1),$B$12:$B$17,0)),"")</f>
-        <v>5</v>
-      </c>
-      <c r="J21" s="41" t="str">
-        <f aca="false">IF(OR(C21="",G21="",I21=""),"",IF(ABS(G21)+N(H21)&lt;=I21+0.000000001,"Aprovado","Reprovado"))</f>
-        <v>Aprovado</v>
-      </c>
-      <c r="K21" s="41"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="17" t="str">
-        <f aca="false">IF(LEFT(C21,FIND(" ·",C21)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C21,FIND(" ·",C21)-1),$B$12:$B$17,0)),"Instrumento não cadastrado",IF(I21="","Falta o critério no cadastro",IF(E21="","Falta o registro",IF(G21="","Falta o erro encontrado",IF(AND(J21="Reprovado",L21=""),"Falta a ação",IF(AND(J21="Reprovado",O21=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
-        <v>OK</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="37" t="n">
-        <v>46407</v>
+        <v>46188</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D22" s="34" t="s">
         <v>213</v>
-      </c>
-      <c r="D22" s="34" t="s">
-        <v>211</v>
       </c>
       <c r="E22" s="40" t="s">
         <v>214</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I22" s="23" t="n">
+        <f aca="false">IFERROR(INDEX($L$12:$L$18,MATCH(LEFT(C22,FIND(" ·",C22)-1),$B$12:$B$18,0)),"")</f>
         <v>5</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="23" t="n">
-        <f aca="false">IFERROR(INDEX($L$12:$L$17,MATCH(LEFT(C22,FIND(" ·",C22)-1),$B$12:$B$17,0)),"")</f>
-        <v>10</v>
       </c>
       <c r="J22" s="41" t="str">
         <f aca="false">IF(OR(C22="",G22="",I22=""),"",IF(ABS(G22)+N(H22)&lt;=I22+0.000000001,"Aprovado","Reprovado"))</f>
@@ -7902,33 +7926,33 @@
       <c r="O22" s="40"/>
       <c r="P22" s="40"/>
       <c r="Q22" s="17" t="str">
-        <f aca="false">IF(LEFT(C22,FIND(" ·",C22)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C22,FIND(" ·",C22)-1),$B$12:$B$17,0)),"Instrumento não cadastrado",IF(I22="","Falta o critério no cadastro",IF(E22="","Falta o registro",IF(G22="","Falta o erro encontrado",IF(AND(J22="Reprovado",L22=""),"Falta a ação",IF(AND(J22="Reprovado",O22=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
+        <f aca="false">IF(LEFT(C22,FIND(" ·",C22)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C22,FIND(" ·",C22)-1),$B$12:$B$18,0)),"Instrumento não cadastrado",IF(I22="","Falta o critério no cadastro",IF(E22="","Falta o registro",IF(G22="","Falta o erro encontrado",IF(AND(J22="Reprovado",L22=""),"Falta a ação",IF(AND(J22="Reprovado",O22=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
         <v>OK</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="37" t="n">
-        <v>46447</v>
+        <v>46407</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>215</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="E23" s="40" t="s">
         <v>216</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H23" s="35" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="I23" s="23" t="n">
-        <f aca="false">IFERROR(INDEX($L$12:$L$17,MATCH(LEFT(C23,FIND(" ·",C23)-1),$B$12:$B$17,0)),"")</f>
-        <v>2</v>
+        <f aca="false">IFERROR(INDEX($L$12:$L$18,MATCH(LEFT(C23,FIND(" ·",C23)-1),$B$12:$B$18,0)),"")</f>
+        <v>10</v>
       </c>
       <c r="J23" s="41" t="str">
         <f aca="false">IF(OR(C23="",G23="",I23=""),"",IF(ABS(G23)+N(H23)&lt;=I23+0.000000001,"Aprovado","Reprovado"))</f>
@@ -7941,13 +7965,13 @@
       <c r="O23" s="40"/>
       <c r="P23" s="40"/>
       <c r="Q23" s="17" t="str">
-        <f aca="false">IF(LEFT(C23,FIND(" ·",C23)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C23,FIND(" ·",C23)-1),$B$12:$B$17,0)),"Instrumento não cadastrado",IF(I23="","Falta o critério no cadastro",IF(E23="","Falta o registro",IF(G23="","Falta o erro encontrado",IF(AND(J23="Reprovado",L23=""),"Falta a ação",IF(AND(J23="Reprovado",O23=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
+        <f aca="false">IF(LEFT(C23,FIND(" ·",C23)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C23,FIND(" ·",C23)-1),$B$12:$B$18,0)),"Instrumento não cadastrado",IF(I23="","Falta o critério no cadastro",IF(E23="","Falta o registro",IF(G23="","Falta o erro encontrado",IF(AND(J23="Reprovado",L23=""),"Falta a ação",IF(AND(J23="Reprovado",O23=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
         <v>OK</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="37" t="n">
-        <v>46451</v>
+        <v>46447</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>217</v>
@@ -7960,14 +7984,14 @@
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="35" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H24" s="35" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I24" s="23" t="n">
-        <f aca="false">IFERROR(INDEX($L$12:$L$17,MATCH(LEFT(C24,FIND(" ·",C24)-1),$B$12:$B$17,0)),"")</f>
-        <v>1</v>
+        <f aca="false">IFERROR(INDEX($L$12:$L$18,MATCH(LEFT(C24,FIND(" ·",C24)-1),$B$12:$B$18,0)),"")</f>
+        <v>2</v>
       </c>
       <c r="J24" s="41" t="str">
         <f aca="false">IF(OR(C24="",G24="",I24=""),"",IF(ABS(G24)+N(H24)&lt;=I24+0.000000001,"Aprovado","Reprovado"))</f>
@@ -7980,13 +8004,13 @@
       <c r="O24" s="40"/>
       <c r="P24" s="40"/>
       <c r="Q24" s="17" t="str">
-        <f aca="false">IF(LEFT(C24,FIND(" ·",C24)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C24,FIND(" ·",C24)-1),$B$12:$B$17,0)),"Instrumento não cadastrado",IF(I24="","Falta o critério no cadastro",IF(E24="","Falta o registro",IF(G24="","Falta o erro encontrado",IF(AND(J24="Reprovado",L24=""),"Falta a ação",IF(AND(J24="Reprovado",O24=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
+        <f aca="false">IF(LEFT(C24,FIND(" ·",C24)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C24,FIND(" ·",C24)-1),$B$12:$B$18,0)),"Instrumento não cadastrado",IF(I24="","Falta o critério no cadastro",IF(E24="","Falta o registro",IF(G24="","Falta o erro encontrado",IF(AND(J24="Reprovado",L24=""),"Falta a ação",IF(AND(J24="Reprovado",O24=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="37" t="n">
-        <v>46461</v>
+        <v>46451</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>219</v>
@@ -7999,107 +8023,139 @@
       </c>
       <c r="F25" s="40"/>
       <c r="G25" s="35" t="n">
-        <v>-2</v>
+        <v>0.3</v>
       </c>
       <c r="H25" s="35" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I25" s="23" t="n">
-        <f aca="false">IFERROR(INDEX($L$12:$L$17,MATCH(LEFT(C25,FIND(" ·",C25)-1),$B$12:$B$17,0)),"")</f>
+        <f aca="false">IFERROR(INDEX($L$12:$L$18,MATCH(LEFT(C25,FIND(" ·",C25)-1),$B$12:$B$18,0)),"")</f>
         <v>1</v>
       </c>
       <c r="J25" s="41" t="str">
         <f aca="false">IF(OR(C25="",G25="",I25=""),"",IF(ABS(G25)+N(H25)&lt;=I25+0.000000001,"Aprovado","Reprovado"))</f>
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
       <c r="K25" s="41"/>
-      <c r="L25" s="40" t="s">
-        <v>221</v>
-      </c>
+      <c r="L25" s="40"/>
       <c r="M25" s="40"/>
       <c r="N25" s="40"/>
       <c r="O25" s="40"/>
       <c r="P25" s="40"/>
       <c r="Q25" s="17" t="str">
-        <f aca="false">IF(LEFT(C25,FIND(" ·",C25)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C25,FIND(" ·",C25)-1),$B$12:$B$17,0)),"Instrumento não cadastrado",IF(I25="","Falta o critério no cadastro",IF(E25="","Falta o registro",IF(G25="","Falta o erro encontrado",IF(AND(J25="Reprovado",L25=""),"Falta a ação",IF(AND(J25="Reprovado",O25=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
+        <f aca="false">IF(LEFT(C25,FIND(" ·",C25)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C25,FIND(" ·",C25)-1),$B$12:$B$18,0)),"Instrumento não cadastrado",IF(I25="","Falta o critério no cadastro",IF(E25="","Falta o registro",IF(G25="","Falta o erro encontrado",IF(AND(J25="Reprovado",L25=""),"Falta a ação",IF(AND(J25="Reprovado",O25=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="37" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="F26" s="40"/>
+      <c r="G26" s="35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I26" s="23" t="n">
+        <f aca="false">IFERROR(INDEX($L$12:$L$18,MATCH(LEFT(C26,FIND(" ·",C26)-1),$B$12:$B$18,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="J26" s="41" t="str">
+        <f aca="false">IF(OR(C26="",G26="",I26=""),"",IF(ABS(G26)+N(H26)&lt;=I26+0.000000001,"Aprovado","Reprovado"))</f>
+        <v>Reprovado</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="40"/>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="17" t="str">
+        <f aca="false">IF(LEFT(C26,FIND(" ·",C26)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C26,FIND(" ·",C26)-1),$B$12:$B$18,0)),"Instrumento não cadastrado",IF(I26="","Falta o critério no cadastro",IF(E26="","Falta o registro",IF(G26="","Falta o erro encontrado",IF(AND(J26="Reprovado",L26=""),"Falta a ação",IF(AND(J26="Reprovado",O26=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
         <v>Falta avaliar os resultados anteriores</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="18" t="s">
+    <row r="27" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="37" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="F27" s="40"/>
+      <c r="G27" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I27" s="23" t="n">
+        <f aca="false">IFERROR(INDEX($L$12:$L$18,MATCH(LEFT(C27,FIND(" ·",C27)-1),$B$12:$B$18,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="J27" s="41" t="str">
+        <f aca="false">IF(OR(C27="",G27="",I27=""),"",IF(ABS(G27)+N(H27)&lt;=I27+0.000000001,"Aprovado","Reprovado"))</f>
+        <v>Aprovado</v>
+      </c>
+      <c r="K27" s="41"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="17" t="str">
+        <f aca="false">IF(LEFT(C27,FIND(" ·",C27)-1)="",IF(1&gt;0,"Falta o instrumento",""),IF(ISNA(MATCH(LEFT(C27,FIND(" ·",C27)-1),$B$12:$B$18,0)),"Instrumento não cadastrado",IF(I27="","Falta o critério no cadastro",IF(E27="","Falta o registro",IF(G27="","Falta o erro encontrado",IF(AND(J27="Reprovado",L27=""),"Falta a ação",IF(AND(J27="Reprovado",O27=""),"Falta avaliar os resultados anteriores","OK")))))))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="18"/>
-    </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="20" t="str">
-        <f aca="false">COUNTIF(O12:O17,"Em dia")&amp;" em dia"&amp;", "&amp;COUNTIF(O12:O17,"Vence em 30 dias")&amp;" vence em 30 dias"&amp;", "&amp;COUNTIF(O12:O17,"Vencido")&amp;" vencido"&amp;", "&amp;COUNTIF(O12:O17,"Sem calibração")&amp;" sem calibração"&amp;", "&amp;COUNTIF(O12:O17,"Fora de uso")&amp;" fora de uso"</f>
-        <v>2 em dia, 2 vence em 30 dias, 0 vencido, 1 sem calibração, 1 fora de uso</v>
-      </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="20" t="n">
-        <f aca="false">COUNTIF(P12:P17,"Resolução grossa")</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
       <c r="E30" s="20" t="str">
-        <f aca="false">COUNTIF(J21:J25,"Aprovado")&amp;" aprovados, "&amp;COUNTIF(J21:J25,"Reprovado")&amp;" reprovados"</f>
-        <v>4 aprovados, 1 reprovados</v>
+        <f aca="false">COUNTIF(O12:O18,"Em dia")&amp;" em dia"&amp;", "&amp;COUNTIF(O12:O18,"Vence em breve")&amp;" vence em breve"&amp;", "&amp;COUNTIF(O12:O18,"Vencido")&amp;" vencido"&amp;", "&amp;COUNTIF(O12:O18,"Sem calibração")&amp;" sem calibração"&amp;", "&amp;COUNTIF(O12:O18,"Fora de uso")&amp;" fora de uso"</f>
+        <v>3 em dia, 2 vence em breve, 0 vencido, 1 sem calibração, 1 fora de uso</v>
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
@@ -8116,13 +8172,13 @@
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="19" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
       <c r="E31" s="20" t="n">
-        <f aca="false">SUMPRODUCT((Q21:Q25&lt;&gt;"OK")*1)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(P12:P18,"Resolução grossa")</f>
+        <v>0</v>
       </c>
       <c r="F31" s="20"/>
       <c r="G31" s="20"/>
@@ -8137,8 +8193,54 @@
       <c r="P31" s="20"/>
       <c r="Q31" s="20"/>
     </row>
+    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20" t="str">
+        <f aca="false">COUNTIF(J22:J27,"Aprovado")&amp;" aprovados, "&amp;COUNTIF(J22:J27,"Reprovado")&amp;" reprovados"</f>
+        <v>5 aprovados, 1 reprovados</v>
+      </c>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="20" t="n">
+        <f aca="false">SUMPRODUCT((Q22:Q27&lt;&gt;"OK")*1)</f>
+        <v>1</v>
+      </c>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="50">
     <mergeCell ref="B1:Q1"/>
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B4:C4"/>
@@ -8151,11 +8253,7 @@
     <mergeCell ref="D7:Q7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B10:Q10"/>
-    <mergeCell ref="B19:Q19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="B20:Q20"/>
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
@@ -8176,22 +8274,30 @@
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:P25"/>
-    <mergeCell ref="B27:Q27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:Q28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:Q29"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="B29:Q29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="E30:Q30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="E31:Q31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:Q32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:Q33"/>
   </mergeCells>
-  <conditionalFormatting sqref="O12:O17">
+  <conditionalFormatting sqref="O12:O18">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>O12="Em dia"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>O12="Vence em 30 dias"</formula>
+      <formula>O12="Vence em breve"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>O12="Vencido"</formula>
@@ -8203,7 +8309,7 @@
       <formula>O12="Fora de uso"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P12:P17">
+  <conditionalFormatting sqref="P12:P18">
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>P12="Adequado"</formula>
     </cfRule>
@@ -8211,7 +8317,7 @@
       <formula>P12="Resolução grossa"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q12:Q17">
+  <conditionalFormatting sqref="Q12:Q18">
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>OR(Q12="OK",Q12="Fora de uso")</formula>
     </cfRule>
@@ -8219,23 +8325,23 @@
       <formula>AND(LEN(Q12)&gt;0,NOT(OR(Q12="OK",Q12="Fora de uso")))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J21:K25">
+  <conditionalFormatting sqref="J22:K27">
     <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$J21="Aprovado"</formula>
+      <formula>$J22="Aprovado"</formula>
     </cfRule>
     <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>$J21="Reprovado"</formula>
+      <formula>$J22="Reprovado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q21:Q25">
+  <conditionalFormatting sqref="Q22:Q27">
     <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>Q21="OK"</formula>
+      <formula>Q22="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>Q21="Falta avaliar os resultados anteriores"</formula>
+      <formula>Q22="Falta avaliar os resultados anteriores"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>LEN(Q21)&gt;0</formula>
+      <formula>LEN(Q22)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
@@ -8246,7 +8352,7 @@
     <oddFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="18" man="true" max="16383" min="0"/>
+    <brk id="19" man="true" max="16383" min="0"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -8324,7 +8430,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="29" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E4" s="29"/>
       <c r="F4" s="29"/>
@@ -8346,7 +8452,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="29" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E5" s="29"/>
       <c r="F5" s="29"/>
@@ -8368,7 +8474,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="29" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
@@ -8390,7 +8496,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="29" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E7" s="29"/>
       <c r="F7" s="29"/>
@@ -8487,19 +8593,19 @@
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="32" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G12" s="35" t="n">
         <v>4</v>
@@ -8527,7 +8633,7 @@
         <v>46733</v>
       </c>
       <c r="O12" s="16" t="str">
-        <f aca="false">IF(B12="","",IF(M12="Não","Fora de uso",IF(K12="","Sem calibração",IF(AND(ISNUMBER($D$8),N12&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N12-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B12="","",IF(M12="Não","Fora de uso",IF(K12="","Sem calibração",IF(AND(ISNUMBER($D$8),N12&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N12-$D$8&lt;MIN(30,(N12-K12)/4)),"Vence em breve","Em dia")))))</f>
         <v>Fora de uso</v>
       </c>
       <c r="P12" s="17" t="str">
@@ -8541,19 +8647,19 @@
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="32" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C13" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="F13" s="34" t="s">
         <v>235</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>232</v>
       </c>
       <c r="G13" s="35" t="n">
         <v>4</v>
@@ -8581,7 +8687,7 @@
         <v>46645</v>
       </c>
       <c r="O13" s="16" t="str">
-        <f aca="false">IF(B13="","",IF(M13="Não","Fora de uso",IF(K13="","Sem calibração",IF(AND(ISNUMBER($D$8),N13&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N13-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B13="","",IF(M13="Não","Fora de uso",IF(K13="","Sem calibração",IF(AND(ISNUMBER($D$8),N13&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N13-$D$8&lt;MIN(30,(N13-K13)/4)),"Vence em breve","Em dia")))))</f>
         <v>Em dia</v>
       </c>
       <c r="P13" s="17" t="str">
@@ -8595,19 +8701,19 @@
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="32" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G14" s="35" t="n">
         <v>4</v>
@@ -8635,7 +8741,7 @@
         <v>46699</v>
       </c>
       <c r="O14" s="16" t="str">
-        <f aca="false">IF(B14="","",IF(M14="Não","Fora de uso",IF(K14="","Sem calibração",IF(AND(ISNUMBER($D$8),N14&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N14-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B14="","",IF(M14="Não","Fora de uso",IF(K14="","Sem calibração",IF(AND(ISNUMBER($D$8),N14&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N14-$D$8&lt;MIN(30,(N14-K14)/4)),"Vence em breve","Em dia")))))</f>
         <v>Em dia</v>
       </c>
       <c r="P14" s="17" t="str">
@@ -8649,16 +8755,16 @@
     </row>
     <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="32" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F15" s="34" t="s">
         <v>181</v>
@@ -8689,7 +8795,7 @@
         <v>46601</v>
       </c>
       <c r="O15" s="16" t="str">
-        <f aca="false">IF(B15="","",IF(M15="Não","Fora de uso",IF(K15="","Sem calibração",IF(AND(ISNUMBER($D$8),N15&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N15-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B15="","",IF(M15="Não","Fora de uso",IF(K15="","Sem calibração",IF(AND(ISNUMBER($D$8),N15&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N15-$D$8&lt;MIN(30,(N15-K15)/4)),"Vence em breve","Em dia")))))</f>
         <v>Em dia</v>
       </c>
       <c r="P15" s="17" t="str">
@@ -8703,19 +8809,19 @@
     </row>
     <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="32" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G16" s="35" t="n">
         <v>2</v>
@@ -8743,7 +8849,7 @@
         <v>46894</v>
       </c>
       <c r="O16" s="16" t="str">
-        <f aca="false">IF(B16="","",IF(M16="Não","Fora de uso",IF(K16="","Sem calibração",IF(AND(ISNUMBER($D$8),N16&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N16-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B16="","",IF(M16="Não","Fora de uso",IF(K16="","Sem calibração",IF(AND(ISNUMBER($D$8),N16&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N16-$D$8&lt;MIN(30,(N16-K16)/4)),"Vence em breve","Em dia")))))</f>
         <v>Em dia</v>
       </c>
       <c r="P16" s="17" t="str">
@@ -8757,16 +8863,16 @@
     </row>
     <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="32" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F17" s="34" t="s">
         <v>181</v>
@@ -8797,7 +8903,7 @@
         <v>46553</v>
       </c>
       <c r="O17" s="16" t="str">
-        <f aca="false">IF(B17="","",IF(M17="Não","Fora de uso",IF(K17="","Sem calibração",IF(AND(ISNUMBER($D$8),N17&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N17-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B17="","",IF(M17="Não","Fora de uso",IF(K17="","Sem calibração",IF(AND(ISNUMBER($D$8),N17&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N17-$D$8&lt;MIN(30,(N17-K17)/4)),"Vence em breve","Em dia")))))</f>
         <v>Vencido</v>
       </c>
       <c r="P17" s="17" t="str">
@@ -8811,16 +8917,16 @@
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="32" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F18" s="34" t="s">
         <v>181</v>
@@ -8849,7 +8955,7 @@
         <v>46793</v>
       </c>
       <c r="O18" s="16" t="str">
-        <f aca="false">IF(B18="","",IF(M18="Não","Fora de uso",IF(K18="","Sem calibração",IF(AND(ISNUMBER($D$8),N18&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N18-$D$8&lt;=30),"Vence em 30 dias","Em dia")))))</f>
+        <f aca="false">IF(B18="","",IF(M18="Não","Fora de uso",IF(K18="","Sem calibração",IF(AND(ISNUMBER($D$8),N18&lt;$D$8),"Vencido",IF(AND(ISNUMBER($D$8),N18-$D$8&lt;MIN(30,(N18-K18)/4)),"Vence em breve","Em dia")))))</f>
         <v>Em dia</v>
       </c>
       <c r="P18" s="17" t="str">
@@ -8886,13 +8992,13 @@
         <v>91</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" s="25" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F21" s="39"/>
       <c r="G21" s="25" t="s">
@@ -8909,12 +9015,12 @@
       </c>
       <c r="K21" s="39"/>
       <c r="L21" s="39" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M21" s="39"/>
       <c r="N21" s="39"/>
       <c r="O21" s="39" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P21" s="39"/>
       <c r="Q21" s="25" t="s">
@@ -8926,13 +9032,13 @@
         <v>46236</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="35" t="n">
@@ -8965,13 +9071,13 @@
         <v>46334</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="35" t="n">
@@ -9004,20 +9110,20 @@
         <v>46397</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H24" s="35" t="n">
         <v>0.6</v>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>0.3</v>
       </c>
       <c r="I24" s="23" t="n">
         <f aca="false">IFERROR(INDEX($L$12:$L$18,MATCH(LEFT(C24,FIND(" ·",C24)-1),$B$12:$B$18,0)),"")</f>
@@ -9043,13 +9149,13 @@
         <v>46428</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F25" s="40"/>
       <c r="G25" s="35" t="n">
@@ -9082,13 +9188,13 @@
         <v>46461</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="35" t="n">
@@ -9121,13 +9227,13 @@
         <v>46461</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D27" s="34" t="s">
         <v>117</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="35" t="n">
@@ -9160,13 +9266,13 @@
         <v>46528</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="35" t="n">
@@ -9199,20 +9305,20 @@
         <v>46550</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D29" s="34" t="s">
         <v>117</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="35" t="n">
         <v>1.6</v>
       </c>
       <c r="H29" s="35" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">IFERROR(INDEX($L$12:$L$18,MATCH(LEFT(C29,FIND(" ·",C29)-1),$B$12:$B$18,0)),"")</f>
@@ -9224,12 +9330,12 @@
       </c>
       <c r="K29" s="41"/>
       <c r="L29" s="40" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M29" s="40"/>
       <c r="N29" s="40"/>
       <c r="O29" s="40" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="P29" s="40"/>
       <c r="Q29" s="17" t="str">
@@ -9259,13 +9365,13 @@
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="19" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="20" t="str">
-        <f aca="false">COUNTIF(O12:O18,"Em dia")&amp;" em dia"&amp;", "&amp;COUNTIF(O12:O18,"Vence em 30 dias")&amp;" vence em 30 dias"&amp;", "&amp;COUNTIF(O12:O18,"Vencido")&amp;" vencido"&amp;", "&amp;COUNTIF(O12:O18,"Sem calibração")&amp;" sem calibração"&amp;", "&amp;COUNTIF(O12:O18,"Fora de uso")&amp;" fora de uso"</f>
-        <v>5 em dia, 0 vence em 30 dias, 1 vencido, 0 sem calibração, 1 fora de uso</v>
+        <f aca="false">COUNTIF(O12:O18,"Em dia")&amp;" em dia"&amp;", "&amp;COUNTIF(O12:O18,"Vence em breve")&amp;" vence em breve"&amp;", "&amp;COUNTIF(O12:O18,"Vencido")&amp;" vencido"&amp;", "&amp;COUNTIF(O12:O18,"Sem calibração")&amp;" sem calibração"&amp;", "&amp;COUNTIF(O12:O18,"Fora de uso")&amp;" fora de uso"</f>
+        <v>5 em dia, 0 vence em breve, 1 vencido, 0 sem calibração, 1 fora de uso</v>
       </c>
       <c r="F32" s="20"/>
       <c r="G32" s="20"/>
@@ -9305,7 +9411,7 @@
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="19" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
@@ -9415,7 +9521,7 @@
       <formula>O12="Em dia"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>O12="Vence em 30 dias"</formula>
+      <formula>O12="Vence em breve"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>O12="Vencido"</formula>

--- a/Calibracao/Calibracao-modelo.xlsx
+++ b/Calibracao/Calibracao-modelo.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Em dia</t>
   </si>
   <si>
-    <t xml:space="preserve">Até a próxima data faltam mais dias do que o aviso: um quarto do intervalo, com no máximo 30 dias.</t>
+    <t xml:space="preserve">Até a próxima data faltam tantos dias quanto o aviso, ou mais: um quarto do intervalo, com no máximo 30 dias.</t>
   </si>
   <si>
     <t xml:space="preserve">Vence em breve</t>
@@ -492,7 +492,7 @@
     <t xml:space="preserve">Da aba Instrumentos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mais longe do que o aviso: um quarto do intervalo, no máximo 30 dias.</t>
+    <t xml:space="preserve">Faltam tantos dias quanto o aviso, ou mais: um quarto do intervalo, no máximo 30 dias.</t>
   </si>
   <si>
     <t xml:space="preserve">Programar a calibração ou a verificação.</t>
@@ -1539,11 +1539,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="7906842"/>
-        <c:axId val="70901307"/>
+        <c:axId val="97683038"/>
+        <c:axId val="72540678"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="7906842"/>
+        <c:axId val="97683038"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1575,7 +1575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70901307"/>
+        <c:crossAx val="72540678"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1583,7 +1583,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70901307"/>
+        <c:axId val="72540678"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1623,7 +1623,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7906842"/>
+        <c:crossAx val="97683038"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
